--- a/data/Diessenhofen/investment_decision/Diessenhofen_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Diessenhofen_SFH_2005-2014_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>30.99917904173038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>38947.45496787146</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>30.99917904173038</v>
       </c>
       <c r="G2" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.503088383232799</v>
       </c>
       <c r="I2" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.503088383232799</v>
       </c>
       <c r="K2" t="n">
         <v>38947.45496787146</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>59.90937455286419</v>
+        <v>30.99917904173038</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>38947.45496787146</v>
       </c>
       <c r="F3" t="n">
-        <v>59.90937455286419</v>
+        <v>30.99917904173038</v>
       </c>
       <c r="G3" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="H3" t="n">
-        <v>64.4074174567379</v>
+        <v>28.64801790318196</v>
       </c>
       <c r="I3" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="J3" t="n">
-        <v>64.4074174567379</v>
+        <v>28.64801790318195</v>
       </c>
       <c r="K3" t="n">
         <v>38947.45496787146</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>153.1098210991561</v>
+        <v>209.7622726451607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>38947.45496787146</v>
       </c>
       <c r="F4" t="n">
-        <v>157.8253317621105</v>
+        <v>209.7622726451607</v>
       </c>
       <c r="G4" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="H4" t="n">
-        <v>151.7300509678251</v>
+        <v>209.7622726451608</v>
       </c>
       <c r="I4" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="J4" t="n">
-        <v>151.7300509678251</v>
+        <v>208.4352881352887</v>
       </c>
       <c r="K4" t="n">
         <v>38947.45496787146</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>178.1443990247591</v>
+        <v>249.230500583944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>38947.45496787146</v>
       </c>
       <c r="F5" t="n">
-        <v>166.0012204113302</v>
+        <v>248.902006860639</v>
       </c>
       <c r="G5" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="H5" t="n">
-        <v>162.6351669724503</v>
+        <v>249.2305005839438</v>
       </c>
       <c r="I5" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="J5" t="n">
-        <v>162.6351669724503</v>
+        <v>246.2994392090693</v>
       </c>
       <c r="K5" t="n">
         <v>38947.45496787146</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>178.1443990247591</v>
+        <v>249.230500583944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>38947.45496787146</v>
       </c>
       <c r="F6" t="n">
-        <v>166.0012204113302</v>
+        <v>248.902006860639</v>
       </c>
       <c r="G6" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="H6" t="n">
-        <v>162.6351669724503</v>
+        <v>249.2305005839438</v>
       </c>
       <c r="I6" t="n">
         <v>38947.45496787146</v>
       </c>
       <c r="J6" t="n">
-        <v>162.6351669724503</v>
+        <v>246.2994392090693</v>
       </c>
       <c r="K6" t="n">
         <v>38947.45496787146</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>34.11226242967051</v>
+        <v>49.58965504236989</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34.11226242967051</v>
+        <v>49.58965504236989</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>45.27603187133921</v>
+        <v>65.8186423962951</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>45.27603187133921</v>
+        <v>65.8186423962951</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>50.15109917129398</v>
+        <v>72.90562193075192</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>50.15109917129398</v>
+        <v>72.90562193075192</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>52.68498148544199</v>
+        <v>76.58917561282225</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>52.68498148544199</v>
+        <v>76.58917561282225</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>58.4211824518072</v>
+        <v>84.9280017977528</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>54.1625115880131</v>
+        <v>78.73708967311889</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>54.1625115880131</v>
+        <v>78.73708967311889</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01257648107294118</v>
+        <v>0.008003215228235296</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01257648107294118</v>
+        <v>0.008574873458823528</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01257648107294118</v>
+        <v>0.009146531689411765</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01257648107294118</v>
+        <v>0.009146531689411765</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01314813930352941</v>
+        <v>0.01028984815058823</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01314813930352941</v>
+        <v>0.01028984815058823</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01314813930352941</v>
+        <v>0.01031716393308179</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01314813930352941</v>
+        <v>0.01031746031746032</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01314813930352941</v>
+        <v>0.01200482284235294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01314813930352941</v>
+        <v>0.01200482284235294</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01355241928470588</v>
+        <v>0.01200482284235294</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01355241928470588</v>
+        <v>0.01248797436063064</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01297325962505251</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01313809966362669</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01297325962505251</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01257648107294118</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01297325962505251</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01313809966362669</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01297325962505251</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01543477222588235</v>
+        <v>0.01257648107294118</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.023163641009473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>10.204099416</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.023163641009472</v>
       </c>
       <c r="G19" t="n">
         <v>10.204099416</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.023163641009472</v>
       </c>
       <c r="I19" t="n">
         <v>10.204099416</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.039061107852056</v>
       </c>
       <c r="K19" t="n">
         <v>10.204099416</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1.655029169907722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>10.204099416</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.694520108260301</v>
       </c>
       <c r="G20" t="n">
         <v>10.204099416</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.242581653869765</v>
       </c>
       <c r="I20" t="n">
         <v>10.204099416</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.26847145379339</v>
       </c>
       <c r="K20" t="n">
         <v>10.204099416</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1.655029169907722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>10.204099416</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.694520108260301</v>
       </c>
       <c r="G21" t="n">
         <v>10.204099416</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.242581653869765</v>
       </c>
       <c r="I21" t="n">
         <v>10.204099416</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.26847145379339</v>
       </c>
       <c r="K21" t="n">
         <v>10.204099416</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.03834726267742063</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>10.204099416</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.005333558698322079</v>
       </c>
       <c r="G30" t="n">
         <v>10.204099416</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.3301749322576639</v>
       </c>
       <c r="I30" t="n">
         <v>10.204099416</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.336866851352714</v>
       </c>
       <c r="K30" t="n">
         <v>10.204099416</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.190999048695996</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>10.204099416</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.1657507409724775</v>
       </c>
       <c r="G31" t="n">
         <v>10.204099416</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.5428863222419619</v>
       </c>
       <c r="I31" t="n">
         <v>10.204099416</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.5784808138372711</v>
       </c>
       <c r="K31" t="n">
         <v>10.204099416</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>12.16831811018615</v>
+        <v>12.33723284672078</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>67.10848242359856</v>
       </c>
       <c r="F54" t="n">
-        <v>11.96464583043083</v>
+        <v>11.99759161253293</v>
       </c>
       <c r="G54" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="H54" t="n">
-        <v>11.87537761776129</v>
+        <v>11.98261662314868</v>
       </c>
       <c r="I54" t="n">
         <v>40.67819525121438</v>
       </c>
       <c r="J54" t="n">
-        <v>12.17667915758576</v>
+        <v>11.96549310026071</v>
       </c>
       <c r="K54" t="n">
         <v>40.67819525121438</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>13.49022117230199</v>
+        <v>14.08158060766577</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>67.10848242359856</v>
       </c>
       <c r="F55" t="n">
-        <v>12.85876529651656</v>
+        <v>13.60651053354396</v>
       </c>
       <c r="G55" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="H55" t="n">
-        <v>12.67417557570842</v>
+        <v>14.08158060766576</v>
       </c>
       <c r="I55" t="n">
         <v>44.93660917207914</v>
       </c>
       <c r="J55" t="n">
-        <v>13.22173626245666</v>
+        <v>13.04578409441297</v>
       </c>
       <c r="K55" t="n">
         <v>44.93660917207914</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>13.49022117230199</v>
+        <v>14.08158060766577</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>67.10848242359856</v>
       </c>
       <c r="F56" t="n">
-        <v>12.85876529651656</v>
+        <v>13.60651053354396</v>
       </c>
       <c r="G56" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="H56" t="n">
-        <v>12.67417557570842</v>
+        <v>14.08158060766576</v>
       </c>
       <c r="I56" t="n">
         <v>47.84076299069698</v>
       </c>
       <c r="J56" t="n">
-        <v>13.22173626245666</v>
+        <v>13.04578409441297</v>
       </c>
       <c r="K56" t="n">
         <v>47.84076299069698</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>8.812294699370588</v>
+        <v>0.5222148848347478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>67.10848242359856</v>
       </c>
       <c r="F64" t="n">
-        <v>8.911948361560741</v>
+        <v>0.861856119022604</v>
       </c>
       <c r="G64" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="H64" t="n">
-        <v>9.135671297633632</v>
+        <v>0.8768311084068537</v>
       </c>
       <c r="I64" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="J64" t="n">
-        <v>8.834369757809164</v>
+        <v>0.8890369828170568</v>
       </c>
       <c r="K64" t="n">
         <v>67.10848242359856</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>10.93815830066057</v>
+        <v>1.771014118802405</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>67.10848242359856</v>
       </c>
       <c r="F65" t="n">
-        <v>11.83747841056575</v>
+        <v>2.241466103145367</v>
       </c>
       <c r="G65" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="H65" t="n">
-        <v>12.09631931017271</v>
+        <v>1.771014118802411</v>
       </c>
       <c r="I65" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="J65" t="n">
-        <v>11.54875862342447</v>
+        <v>2.906005270083033</v>
       </c>
       <c r="K65" t="n">
         <v>67.10848242359856</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>10.93815830066057</v>
+        <v>1.771014118802405</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>67.10848242359856</v>
       </c>
       <c r="F66" t="n">
-        <v>11.83747841056575</v>
+        <v>2.241466103145367</v>
       </c>
       <c r="G66" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="H66" t="n">
-        <v>12.09631931017271</v>
+        <v>1.771014118802411</v>
       </c>
       <c r="I66" t="n">
         <v>67.10848242359856</v>
       </c>
       <c r="J66" t="n">
-        <v>11.54875862342447</v>
+        <v>2.906005270083033</v>
       </c>
       <c r="K66" t="n">
         <v>67.10848242359856</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2.673446179405377</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2.673446179405377</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>4.579399986407534</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>4.579399986407534</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>6.083192439352565</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>6.083192439352565</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>7.333203082445246</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>7.333203082445246</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>8.405190409433036</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>8.405190409433036</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="77">
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2.673446179405377</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>2.673446179405377</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="78">
@@ -3329,13 +3329,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>4.579399986407534</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>4.579399986407534</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="79">
@@ -3366,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>6.083192439352565</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>6.083192439352565</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>7.333203082445246</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>7.333203082445246</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.405190409433036</v>
+        <v>67.10848242359856</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>8.405190409433036</v>
+        <v>67.10848242359856</v>
       </c>
     </row>
     <row r="82">
